--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$92</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3570" uniqueCount="654">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:45:50+00:00</t>
+    <t>2023-04-26T08:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -326,6 +326,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -400,10 +404,6 @@
     <t>Meta.versionId</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>Observation.meta.lastUpdated</t>
   </si>
   <si>
@@ -456,14 +456,7 @@
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
     <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile:MesObservationWaistCircumference</t>
   </si>
   <si>
     <t>Observation.meta.security</t>
@@ -2378,12 +2371,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP93"/>
+  <dimension ref="A1:AP92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.98046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="34.4453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2805,7 +2798,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>88</v>
@@ -2889,7 +2882,7 @@
         <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>78</v>
@@ -2901,7 +2894,7 @@
         <v>78</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>78</v>
@@ -2912,10 +2905,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2938,13 +2931,13 @@
         <v>78</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2995,7 +2988,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -3019,7 +3012,7 @@
         <v>78</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>78</v>
@@ -3030,14 +3023,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -3056,16 +3049,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3103,19 +3096,19 @@
         <v>78</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -3127,7 +3120,7 @@
         <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
@@ -3139,7 +3132,7 @@
         <v>78</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>78</v>
@@ -3150,10 +3143,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3179,13 +3172,13 @@
         <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3235,7 +3228,7 @@
         <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -3247,7 +3240,7 @@
         <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>78</v>
@@ -3259,7 +3252,7 @@
         <v>78</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>78</v>
@@ -3367,7 +3360,7 @@
         <v>100</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>78</v>
@@ -3379,7 +3372,7 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>78</v>
@@ -3487,7 +3480,7 @@
         <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -3499,7 +3492,7 @@
         <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>78</v>
@@ -3521,7 +3514,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>77</v>
@@ -3583,17 +3576,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="AC10" s="2"/>
-      <c r="AD10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -3605,7 +3600,7 @@
         <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -3617,7 +3612,7 @@
         <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>78</v>
@@ -3628,26 +3623,24 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>7</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>78</v>
@@ -3656,16 +3649,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3673,7 +3666,7 @@
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="S11" t="s" s="2">
         <v>78</v>
@@ -3691,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>78</v>
@@ -3715,7 +3708,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3727,7 +3720,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>78</v>
@@ -3736,10 +3729,10 @@
         <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>78</v>
@@ -3750,10 +3743,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3776,16 +3769,16 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3811,13 +3804,13 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -3835,7 +3828,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3847,7 +3840,7 @@
         <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>78</v>
@@ -3856,10 +3849,10 @@
         <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>78</v>
@@ -3870,10 +3863,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3884,28 +3877,28 @@
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3931,13 +3924,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3955,19 +3948,19 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
@@ -3976,10 +3969,10 @@
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -3990,10 +3983,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4010,22 +4003,22 @@
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4051,13 +4044,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -4075,7 +4068,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -4087,7 +4080,7 @@
         <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -4099,7 +4092,7 @@
         <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>78</v>
@@ -4110,14 +4103,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4136,16 +4129,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4171,13 +4164,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -4195,7 +4188,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -4207,7 +4200,7 @@
         <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
@@ -4219,7 +4212,7 @@
         <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>107</v>
+        <v>182</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>78</v>
@@ -4230,21 +4223,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -4256,16 +4249,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4315,19 +4308,19 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -4339,7 +4332,7 @@
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>78</v>
@@ -4350,14 +4343,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4376,16 +4369,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4423,19 +4416,19 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -4444,10 +4437,10 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -4459,7 +4452,7 @@
         <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -4470,21 +4463,23 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>78</v>
@@ -4496,17 +4491,15 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4543,19 +4536,19 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4567,7 +4560,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
@@ -4579,7 +4572,7 @@
         <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
@@ -4590,13 +4583,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>78</v>
@@ -4618,13 +4611,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4675,7 +4668,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4687,7 +4680,7 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
@@ -4699,7 +4692,7 @@
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -4710,44 +4703,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -4783,19 +4778,19 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4807,7 +4802,7 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -4819,7 +4814,7 @@
         <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
@@ -4830,14 +4825,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4850,25 +4845,23 @@
         <v>78</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4905,19 +4898,19 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4929,22 +4922,22 @@
         <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>78</v>
@@ -4952,14 +4945,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4978,17 +4971,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -5037,7 +5032,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -5049,22 +5044,22 @@
         <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>78</v>
@@ -5072,14 +5067,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5098,20 +5093,18 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -5159,7 +5152,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -5171,19 +5164,19 @@
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>78</v>
@@ -5194,44 +5187,46 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5255,13 +5250,13 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -5279,34 +5274,34 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>78</v>
@@ -5314,10 +5309,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5328,31 +5323,31 @@
         <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5377,58 +5372,56 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>78</v>
@@ -5436,12 +5429,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -5450,7 +5445,7 @@
         <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>89</v>
@@ -5462,19 +5457,19 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5499,29 +5494,31 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5533,7 +5530,7 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -5542,13 +5539,13 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>78</v>
@@ -5559,23 +5556,21 @@
         <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C27" t="s" s="2">
         <v>265</v>
       </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -5584,20 +5579,16 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -5621,13 +5612,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5645,19 +5636,19 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -5666,13 +5657,13 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>78</v>
@@ -5687,14 +5678,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -5706,15 +5697,17 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5751,31 +5744,31 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
@@ -5787,7 +5780,7 @@
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5805,37 +5798,39 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5871,19 +5866,19 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5895,7 +5890,7 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
@@ -5904,10 +5899,10 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>78</v>
@@ -5918,10 +5913,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5929,35 +5924,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -6005,19 +5996,19 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -6026,10 +6017,10 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>78</v>
@@ -6047,14 +6038,14 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -6066,15 +6057,17 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6111,31 +6104,31 @@
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>78</v>
@@ -6147,7 +6140,7 @@
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -6165,43 +6158,45 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>78</v>
@@ -6231,31 +6226,31 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
@@ -6264,10 +6259,10 @@
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -6278,10 +6273,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6289,13 +6284,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>78</v>
@@ -6304,26 +6299,24 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>78</v>
@@ -6365,7 +6358,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -6377,7 +6370,7 @@
         <v>100</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -6386,10 +6379,10 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -6400,10 +6393,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6411,13 +6404,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>78</v>
@@ -6426,24 +6419,26 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>78</v>
@@ -6485,7 +6480,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6497,7 +6492,7 @@
         <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -6506,10 +6501,10 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -6520,10 +6515,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6531,13 +6526,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>78</v>
@@ -6546,26 +6541,26 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O35" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>78</v>
@@ -6607,7 +6602,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6619,7 +6614,7 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
@@ -6628,10 +6623,10 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -6642,10 +6637,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6668,19 +6663,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6729,7 +6724,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6741,7 +6736,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -6750,10 +6745,10 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
@@ -6764,10 +6759,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6790,19 +6785,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6851,7 +6846,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6863,7 +6858,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
@@ -6872,10 +6867,10 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -6886,24 +6881,24 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>78</v>
@@ -6912,19 +6907,19 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6934,7 +6929,7 @@
         <v>78</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>78</v>
@@ -6949,13 +6944,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6973,10 +6968,10 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>88</v>
@@ -6985,37 +6980,37 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>78</v>
+        <v>349</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7034,19 +7029,19 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>352</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -7056,7 +7051,7 @@
         <v>78</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>78</v>
@@ -7071,13 +7066,13 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -7095,10 +7090,10 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>88</v>
@@ -7107,33 +7102,33 @@
         <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>352</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7141,13 +7136,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>78</v>
@@ -7156,20 +7151,18 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
       </c>
@@ -7217,34 +7210,34 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>359</v>
+        <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>78</v>
@@ -7252,21 +7245,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>78</v>
+        <v>368</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
@@ -7278,18 +7271,20 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -7337,34 +7332,34 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>78</v>
@@ -7372,24 +7367,24 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
@@ -7398,19 +7393,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7459,7 +7454,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -7468,25 +7463,25 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>100</v>
+        <v>385</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>226</v>
+        <v>386</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>78</v>
@@ -7494,24 +7489,24 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -7520,20 +7515,18 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>382</v>
+        <v>126</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -7581,7 +7574,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7590,25 +7583,25 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>387</v>
+        <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>388</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>78</v>
@@ -7616,10 +7609,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7630,7 +7623,7 @@
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -7642,18 +7635,20 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>126</v>
+        <v>399</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7701,34 +7696,34 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>403</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>78</v>
@@ -7736,10 +7731,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7750,10 +7745,10 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>78</v>
@@ -7762,19 +7757,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>224</v>
+        <v>410</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7811,59 +7806,59 @@
         <v>78</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>100</v>
+        <v>414</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>78</v>
+        <v>415</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>408</v>
+        <v>78</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>78</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7884,19 +7879,19 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7906,7 +7901,7 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>78</v>
+        <v>421</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>78</v>
@@ -7933,17 +7928,19 @@
         <v>78</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7952,40 +7949,38 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7997,29 +7992,25 @@
         <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>410</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>411</v>
+        <v>105</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -8028,7 +8019,7 @@
         <v>78</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>78</v>
@@ -8067,7 +8058,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>409</v>
+        <v>107</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -8076,28 +8067,28 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>416</v>
+        <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>417</v>
+        <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>419</v>
+        <v>108</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8109,14 +8100,14 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -8128,15 +8119,17 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -8173,31 +8166,31 @@
         <v>78</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
@@ -8209,7 +8202,7 @@
         <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -8227,14 +8220,14 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>78</v>
@@ -8243,21 +8236,23 @@
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>110</v>
+        <v>428</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>111</v>
+        <v>429</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>112</v>
+        <v>430</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -8293,31 +8288,31 @@
         <v>78</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>117</v>
+        <v>433</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
@@ -8326,10 +8321,10 @@
         <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>78</v>
+        <v>434</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>101</v>
+        <v>435</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -8340,10 +8335,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8360,30 +8355,32 @@
         <v>78</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>430</v>
+        <v>167</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>433</v>
+        <v>303</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q50" s="2"/>
+      <c r="Q50" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="R50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8403,13 +8400,13 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>78</v>
+        <v>442</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -8427,7 +8424,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8439,7 +8436,7 @@
         <v>100</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>78</v>
@@ -8448,10 +8445,10 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8462,10 +8459,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8482,32 +8479,30 @@
         <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q51" t="s" s="2">
-        <v>443</v>
-      </c>
+      <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8527,13 +8522,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>444</v>
+        <v>78</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8551,7 +8546,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8563,7 +8558,7 @@
         <v>100</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>78</v>
@@ -8572,10 +8567,10 @@
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
@@ -8586,10 +8581,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8597,7 +8592,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>88</v>
@@ -8612,19 +8607,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>305</v>
+        <v>459</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8673,7 +8668,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -8682,10 +8677,10 @@
         <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>100</v>
+        <v>462</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -8694,10 +8689,10 @@
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8708,10 +8703,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8734,19 +8729,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8795,7 +8790,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8804,10 +8799,10 @@
         <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>464</v>
+        <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -8816,10 +8811,10 @@
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8830,10 +8825,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8841,34 +8836,34 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8893,13 +8888,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>78</v>
+        <v>477</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>78</v>
+        <v>478</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8926,10 +8921,10 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>100</v>
+        <v>479</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
@@ -8938,10 +8933,10 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>455</v>
+        <v>102</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8952,10 +8947,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8969,7 +8964,7 @@
         <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
@@ -8978,20 +8973,16 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>475</v>
+        <v>105</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -9015,13 +9006,13 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>479</v>
+        <v>78</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>480</v>
+        <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -9039,7 +9030,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>474</v>
+        <v>107</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -9048,10 +9039,10 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>481</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
@@ -9060,10 +9051,10 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>482</v>
+        <v>108</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -9074,21 +9065,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -9100,15 +9091,17 @@
         <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -9145,31 +9138,31 @@
         <v>78</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
@@ -9181,7 +9174,7 @@
         <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -9192,14 +9185,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9215,21 +9208,23 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -9265,19 +9260,19 @@
         <v>78</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -9289,7 +9284,7 @@
         <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
@@ -9298,10 +9293,10 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -9312,10 +9307,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9326,7 +9321,7 @@
         <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
@@ -9335,23 +9330,19 @@
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9399,19 +9390,19 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
@@ -9420,10 +9411,10 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -9434,21 +9425,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -9460,15 +9451,17 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9505,31 +9498,31 @@
         <v>78</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -9541,7 +9534,7 @@
         <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -9552,21 +9545,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9575,21 +9568,23 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9625,31 +9620,31 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -9658,10 +9653,10 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9672,10 +9667,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9683,7 +9678,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>88</v>
@@ -9698,20 +9693,18 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9759,7 +9752,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9771,7 +9764,7 @@
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -9780,10 +9773,10 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9794,10 +9787,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9805,7 +9798,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>88</v>
@@ -9820,18 +9813,20 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9879,7 +9874,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9891,7 +9886,7 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9900,10 +9895,10 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9914,10 +9909,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9925,7 +9920,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>88</v>
@@ -9940,19 +9935,19 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O63" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -10001,7 +9996,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -10013,7 +10008,7 @@
         <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -10022,10 +10017,10 @@
         <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -10036,10 +10031,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10062,19 +10057,19 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -10123,7 +10118,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -10135,7 +10130,7 @@
         <v>100</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
@@ -10144,10 +10139,10 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10158,10 +10153,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10184,19 +10179,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -10245,7 +10240,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -10257,7 +10252,7 @@
         <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -10266,10 +10261,10 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10280,21 +10275,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -10303,22 +10298,22 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>331</v>
+        <v>494</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>332</v>
+        <v>495</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>333</v>
+        <v>496</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>334</v>
+        <v>497</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -10343,13 +10338,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>78</v>
+        <v>499</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -10367,49 +10362,49 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>335</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>336</v>
+        <v>501</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>337</v>
+        <v>502</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>495</v>
+        <v>78</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10428,19 +10423,19 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>253</v>
+        <v>505</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10465,13 +10460,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>500</v>
+        <v>78</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>501</v>
+        <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -10489,7 +10484,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10501,33 +10496,33 @@
         <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>502</v>
+        <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10538,7 +10533,7 @@
         <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -10550,20 +10545,18 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>507</v>
+        <v>251</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>511</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -10587,13 +10580,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>78</v>
+        <v>516</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -10611,45 +10604,45 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>78</v>
+        <v>518</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10672,18 +10665,20 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10707,13 +10702,13 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -10731,7 +10726,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10743,33 +10738,33 @@
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>520</v>
+        <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>523</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10792,20 +10787,18 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>253</v>
+        <v>532</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10829,13 +10822,13 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>530</v>
+        <v>78</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10853,7 +10846,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10865,33 +10858,33 @@
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>536</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10914,16 +10907,16 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10973,7 +10966,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10985,33 +10978,33 @@
         <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11022,7 +11015,7 @@
         <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -11034,18 +11027,20 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -11093,45 +11088,45 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>226</v>
+        <v>555</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>547</v>
+        <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>550</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11142,7 +11137,7 @@
         <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -11154,20 +11149,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>552</v>
+        <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>553</v>
+        <v>105</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -11215,19 +11206,19 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>551</v>
+        <v>107</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>557</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
@@ -11236,10 +11227,10 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>558</v>
+        <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>559</v>
+        <v>108</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -11250,21 +11241,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -11276,15 +11267,17 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -11321,31 +11314,31 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -11357,7 +11350,7 @@
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -11368,14 +11361,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>109</v>
+        <v>561</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11388,24 +11381,26 @@
         <v>78</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>111</v>
+        <v>562</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>112</v>
+        <v>563</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
@@ -11441,19 +11436,19 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>117</v>
+        <v>564</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11465,7 +11460,7 @@
         <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -11477,7 +11472,7 @@
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -11488,46 +11483,44 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>563</v>
+        <v>78</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>566</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -11575,19 +11568,19 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>100</v>
+        <v>570</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>118</v>
+        <v>571</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11596,10 +11589,10 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>78</v>
+        <v>572</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>101</v>
+        <v>573</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11610,10 +11603,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11636,16 +11629,16 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11695,7 +11688,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11704,22 +11697,22 @@
         <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AJ77" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="AN77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11730,10 +11723,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11756,18 +11749,20 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>568</v>
+        <v>251</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
       </c>
@@ -11791,13 +11786,13 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>78</v>
+        <v>583</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -11815,7 +11810,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11824,22 +11819,22 @@
         <v>88</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>572</v>
+        <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>573</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>78</v>
+        <v>585</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>579</v>
+        <v>502</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>
@@ -11850,10 +11845,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11864,7 +11859,7 @@
         <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11876,19 +11871,19 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11913,13 +11908,13 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -11937,31 +11932,31 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -11972,10 +11967,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11986,7 +11981,7 @@
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
@@ -11998,19 +11993,19 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>253</v>
+        <v>595</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -12035,55 +12030,55 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>589</v>
-      </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>124</v>
+        <v>600</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>504</v>
+        <v>602</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
@@ -12094,10 +12089,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12120,20 +12115,18 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>597</v>
+        <v>104</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -12181,7 +12174,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -12193,7 +12186,7 @@
         <v>100</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>602</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -12202,10 +12195,10 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>78</v>
@@ -12216,10 +12209,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12230,7 +12223,7 @@
         <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
@@ -12239,19 +12232,19 @@
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>103</v>
+        <v>608</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>305</v>
+        <v>611</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12301,19 +12294,19 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -12322,10 +12315,10 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>574</v>
+        <v>612</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>78</v>
@@ -12336,10 +12329,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12362,16 +12355,16 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12421,7 +12414,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -12433,7 +12426,7 @@
         <v>100</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -12442,10 +12435,10 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
@@ -12456,10 +12449,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12473,7 +12466,7 @@
         <v>77</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>78</v>
@@ -12482,18 +12475,20 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>617</v>
+        <v>550</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
@@ -12541,7 +12536,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12553,7 +12548,7 @@
         <v>100</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>226</v>
+        <v>624</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -12562,10 +12557,10 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -12576,10 +12571,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12590,32 +12585,28 @@
         <v>76</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>552</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>623</v>
+        <v>105</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12663,19 +12654,19 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>622</v>
+        <v>107</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>626</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12684,10 +12675,10 @@
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>627</v>
+        <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>628</v>
+        <v>108</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12698,21 +12689,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
@@ -12724,15 +12715,17 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -12769,31 +12762,31 @@
         <v>78</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12805,7 +12798,7 @@
         <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -12816,14 +12809,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>109</v>
+        <v>561</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12836,24 +12829,26 @@
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>111</v>
+        <v>562</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>112</v>
+        <v>563</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12889,19 +12884,19 @@
         <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>117</v>
+        <v>564</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12913,7 +12908,7 @@
         <v>100</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12925,7 +12920,7 @@
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -12936,45 +12931,45 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>563</v>
+        <v>78</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>564</v>
+        <v>631</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>565</v>
+        <v>632</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>113</v>
+        <v>633</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>208</v>
+        <v>634</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -12999,13 +12994,13 @@
         <v>78</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>78</v>
@@ -13023,34 +13018,34 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>566</v>
+        <v>630</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>78</v>
+        <v>635</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>78</v>
+        <v>347</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>101</v>
+        <v>348</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>78</v>
+        <v>349</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>78</v>
@@ -13058,10 +13053,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13069,7 +13064,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>88</v>
@@ -13084,19 +13079,19 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>253</v>
+        <v>637</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>636</v>
+        <v>411</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -13121,13 +13116,13 @@
         <v>78</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>149</v>
+        <v>242</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>345</v>
+        <v>641</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>346</v>
+        <v>642</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
@@ -13145,45 +13140,45 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>100</v>
+        <v>643</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>349</v>
+        <v>416</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>350</v>
+        <v>417</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>78</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13203,22 +13198,22 @@
         <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>639</v>
+        <v>251</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>413</v>
+        <v>476</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -13243,13 +13238,13 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>244</v>
+        <v>147</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>643</v>
+        <v>477</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>644</v>
+        <v>478</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -13267,7 +13262,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -13276,50 +13271,50 @@
         <v>88</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>646</v>
+        <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>418</v>
+        <v>102</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>419</v>
+        <v>480</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>78</v>
@@ -13328,19 +13323,19 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>648</v>
+        <v>494</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>649</v>
+        <v>495</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>650</v>
+        <v>496</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13365,13 +13360,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -13389,49 +13384,49 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>651</v>
+        <v>100</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>101</v>
+        <v>501</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>495</v>
+        <v>78</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13450,19 +13445,19 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>496</v>
+        <v>652</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>497</v>
+        <v>653</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>498</v>
+        <v>553</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>499</v>
+        <v>554</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13487,13 +13482,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>500</v>
+        <v>78</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>501</v>
+        <v>78</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13511,7 +13506,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -13520,154 +13515,32 @@
         <v>77</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>502</v>
+        <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>503</v>
+        <v>556</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>504</v>
+        <v>557</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="P93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP93" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP93">
+  <autoFilter ref="A1:AP92">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13677,7 +13550,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI92">
+  <conditionalFormatting sqref="A2:AI91">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:27:54+00:00</t>
+    <t>2023-04-26T14:43:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T14:43:04+00:00</t>
+    <t>2023-04-27T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T16:49:23+00:00</t>
+    <t>2023-05-02T12:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T12:59:07+00:00</t>
+    <t>2023-05-02T13:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T13:06:55+00:00</t>
+    <t>2023-05-02T14:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:33:57+00:00</t>
+    <t>2023-07-18T09:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:12+00:00</t>
+    <t>2023-07-18T09:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:49+00:00</t>
+    <t>2023-07-18T09:37:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3489" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3489" uniqueCount="602">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:37:51+00:00</t>
+    <t>2023-09-19T16:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,6 +141,10 @@
   </si>
   <si>
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
   </si>
   <si>
     <t>Event</t>
@@ -2355,19 +2359,19 @@
         <v>36</v>
       </c>
       <c r="AJ1" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AK1" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AL1" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AM1" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AN1" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AO1" t="s" s="2">
         <v>36</v>
@@ -2378,10 +2382,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2392,7 +2396,7 @@
         <v>34</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>36</v>
@@ -2401,19 +2405,19 @@
         <v>36</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2463,13 +2467,13 @@
         <v>36</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>36</v>
@@ -2498,10 +2502,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2512,7 +2516,7 @@
         <v>34</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>36</v>
@@ -2521,16 +2525,16 @@
         <v>36</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -2581,19 +2585,19 @@
         <v>36</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="s" s="2">
         <v>36</v>
@@ -2605,7 +2609,7 @@
         <v>36</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO3" t="s" s="2">
         <v>36</v>
@@ -2616,10 +2620,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2630,7 +2634,7 @@
         <v>34</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>36</v>
@@ -2642,13 +2646,13 @@
         <v>36</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2699,13 +2703,13 @@
         <v>36</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>36</v>
@@ -2723,7 +2727,7 @@
         <v>36</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>36</v>
@@ -2734,14 +2738,14 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -2760,16 +2764,16 @@
         <v>36</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2807,19 +2811,19 @@
         <v>36</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>34</v>
@@ -2828,10 +2832,10 @@
         <v>35</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>36</v>
@@ -2843,7 +2847,7 @@
         <v>36</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>36</v>
@@ -2854,10 +2858,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2868,7 +2872,7 @@
         <v>34</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>36</v>
@@ -2877,19 +2881,19 @@
         <v>36</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2939,19 +2943,19 @@
         <v>36</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>36</v>
@@ -2963,7 +2967,7 @@
         <v>36</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>36</v>
@@ -2974,10 +2978,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2988,7 +2992,7 @@
         <v>34</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>36</v>
@@ -2997,19 +3001,19 @@
         <v>36</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3059,19 +3063,19 @@
         <v>36</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>36</v>
@@ -3083,7 +3087,7 @@
         <v>36</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>36</v>
@@ -3094,10 +3098,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3108,7 +3112,7 @@
         <v>34</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>36</v>
@@ -3117,19 +3121,19 @@
         <v>36</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3179,19 +3183,19 @@
         <v>36</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>36</v>
@@ -3203,7 +3207,7 @@
         <v>36</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>36</v>
@@ -3214,10 +3218,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3237,19 +3241,19 @@
         <v>36</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3299,7 +3303,7 @@
         <v>36</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>34</v>
@@ -3308,10 +3312,10 @@
         <v>35</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>36</v>
@@ -3323,7 +3327,7 @@
         <v>36</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>36</v>
@@ -3334,10 +3338,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3357,19 +3361,19 @@
         <v>36</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3395,13 +3399,13 @@
         <v>36</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>36</v>
@@ -3419,7 +3423,7 @@
         <v>36</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>34</v>
@@ -3428,10 +3432,10 @@
         <v>35</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>36</v>
@@ -3440,10 +3444,10 @@
         <v>36</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>36</v>
@@ -3454,10 +3458,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3477,19 +3481,19 @@
         <v>36</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3515,13 +3519,13 @@
         <v>36</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>36</v>
@@ -3539,7 +3543,7 @@
         <v>36</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>34</v>
@@ -3548,10 +3552,10 @@
         <v>35</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>36</v>
@@ -3560,10 +3564,10 @@
         <v>36</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>36</v>
@@ -3574,10 +3578,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3588,28 +3592,28 @@
         <v>34</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3659,19 +3663,19 @@
         <v>36</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>36</v>
@@ -3683,7 +3687,7 @@
         <v>36</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>36</v>
@@ -3694,10 +3698,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3708,7 +3712,7 @@
         <v>34</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>36</v>
@@ -3720,16 +3724,16 @@
         <v>36</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3755,13 +3759,13 @@
         <v>36</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>36</v>
@@ -3779,19 +3783,19 @@
         <v>36</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>36</v>
@@ -3803,7 +3807,7 @@
         <v>36</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>36</v>
@@ -3814,21 +3818,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>36</v>
@@ -3840,16 +3844,16 @@
         <v>36</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3899,19 +3903,19 @@
         <v>36</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>36</v>
@@ -3923,7 +3927,7 @@
         <v>36</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>36</v>
@@ -3934,14 +3938,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3960,16 +3964,16 @@
         <v>36</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4019,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>34</v>
@@ -4043,7 +4047,7 @@
         <v>36</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>36</v>
@@ -4054,14 +4058,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4080,16 +4084,16 @@
         <v>36</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4127,19 +4131,19 @@
         <v>36</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>34</v>
@@ -4148,10 +4152,10 @@
         <v>35</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>36</v>
@@ -4163,7 +4167,7 @@
         <v>36</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>36</v>
@@ -4174,13 +4178,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>36</v>
@@ -4190,7 +4194,7 @@
         <v>34</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>36</v>
@@ -4202,13 +4206,13 @@
         <v>36</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4259,7 +4263,7 @@
         <v>36</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>34</v>
@@ -4268,10 +4272,10 @@
         <v>35</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>36</v>
@@ -4283,7 +4287,7 @@
         <v>36</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>36</v>
@@ -4294,13 +4298,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>36</v>
@@ -4310,7 +4314,7 @@
         <v>34</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>36</v>
@@ -4322,13 +4326,13 @@
         <v>36</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4379,7 +4383,7 @@
         <v>36</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>34</v>
@@ -4388,10 +4392,10 @@
         <v>35</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>36</v>
@@ -4414,14 +4418,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4434,25 +4438,25 @@
         <v>36</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>36</v>
@@ -4489,19 +4493,19 @@
         <v>36</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>34</v>
@@ -4510,10 +4514,10 @@
         <v>35</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>36</v>
@@ -4525,7 +4529,7 @@
         <v>36</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>36</v>
@@ -4536,10 +4540,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4559,20 +4563,20 @@
         <v>36</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>36</v>
@@ -4621,7 +4625,7 @@
         <v>36</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>34</v>
@@ -4630,25 +4634,25 @@
         <v>35</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>36</v>
@@ -4656,14 +4660,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4679,22 +4683,22 @@
         <v>36</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>36</v>
@@ -4743,7 +4747,7 @@
         <v>36</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>34</v>
@@ -4752,22 +4756,22 @@
         <v>35</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>36</v>
@@ -4778,14 +4782,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4801,19 +4805,19 @@
         <v>36</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4863,7 +4867,7 @@
         <v>36</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>34</v>
@@ -4872,22 +4876,22 @@
         <v>35</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>36</v>
@@ -4898,10 +4902,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4909,34 +4913,34 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>36</v>
@@ -4961,13 +4965,13 @@
         <v>36</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>36</v>
@@ -4985,34 +4989,34 @@
         <v>36</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>36</v>
@@ -5020,10 +5024,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5031,13 +5035,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>36</v>
@@ -5046,19 +5050,19 @@
         <v>36</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>36</v>
@@ -5083,29 +5087,29 @@
         <v>36</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>34</v>
@@ -5114,10 +5118,10 @@
         <v>35</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>36</v>
@@ -5126,13 +5130,13 @@
         <v>36</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>36</v>
@@ -5140,26 +5144,26 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>36</v>
@@ -5168,19 +5172,19 @@
         <v>36</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>36</v>
@@ -5205,13 +5209,13 @@
         <v>36</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>36</v>
@@ -5229,7 +5233,7 @@
         <v>36</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>34</v>
@@ -5238,10 +5242,10 @@
         <v>35</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>36</v>
@@ -5250,13 +5254,13 @@
         <v>36</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>36</v>
@@ -5264,10 +5268,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5278,7 +5282,7 @@
         <v>34</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>36</v>
@@ -5290,13 +5294,13 @@
         <v>36</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5347,13 +5351,13 @@
         <v>36</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>36</v>
@@ -5371,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>36</v>
@@ -5382,14 +5386,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5408,16 +5412,16 @@
         <v>36</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5455,19 +5459,19 @@
         <v>36</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>34</v>
@@ -5476,10 +5480,10 @@
         <v>35</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>36</v>
@@ -5491,7 +5495,7 @@
         <v>36</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>36</v>
@@ -5502,10 +5506,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5513,34 +5517,34 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>36</v>
@@ -5589,7 +5593,7 @@
         <v>36</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>34</v>
@@ -5598,10 +5602,10 @@
         <v>35</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>36</v>
@@ -5610,10 +5614,10 @@
         <v>36</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>36</v>
@@ -5624,10 +5628,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5638,7 +5642,7 @@
         <v>34</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>36</v>
@@ -5650,13 +5654,13 @@
         <v>36</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5707,13 +5711,13 @@
         <v>36</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>36</v>
@@ -5731,7 +5735,7 @@
         <v>36</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>36</v>
@@ -5742,14 +5746,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5768,16 +5772,16 @@
         <v>36</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5815,19 +5819,19 @@
         <v>36</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>34</v>
@@ -5836,10 +5840,10 @@
         <v>35</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>36</v>
@@ -5851,7 +5855,7 @@
         <v>36</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>36</v>
@@ -5862,10 +5866,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5873,41 +5877,41 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>36</v>
@@ -5949,19 +5953,19 @@
         <v>36</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>36</v>
@@ -5970,10 +5974,10 @@
         <v>36</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>36</v>
@@ -5984,10 +5988,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5998,7 +6002,7 @@
         <v>34</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>36</v>
@@ -6007,19 +6011,19 @@
         <v>36</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6069,19 +6073,19 @@
         <v>36</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>36</v>
@@ -6090,10 +6094,10 @@
         <v>36</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>36</v>
@@ -6104,10 +6108,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6115,41 +6119,41 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>36</v>
@@ -6191,19 +6195,19 @@
         <v>36</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>36</v>
@@ -6212,10 +6216,10 @@
         <v>36</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>36</v>
@@ -6226,10 +6230,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6240,7 +6244,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>36</v>
@@ -6249,22 +6253,22 @@
         <v>36</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>36</v>
@@ -6313,19 +6317,19 @@
         <v>36</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>36</v>
@@ -6334,10 +6338,10 @@
         <v>36</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>36</v>
@@ -6348,10 +6352,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6362,7 +6366,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>36</v>
@@ -6371,22 +6375,22 @@
         <v>36</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>36</v>
@@ -6435,19 +6439,19 @@
         <v>36</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>36</v>
@@ -6456,10 +6460,10 @@
         <v>36</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>36</v>
@@ -6470,10 +6474,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6484,7 +6488,7 @@
         <v>34</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>36</v>
@@ -6493,22 +6497,22 @@
         <v>36</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>36</v>
@@ -6557,19 +6561,19 @@
         <v>36</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>36</v>
@@ -6578,10 +6582,10 @@
         <v>36</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>36</v>
@@ -6592,45 +6596,45 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>36</v>
@@ -6640,7 +6644,7 @@
         <v>36</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>36</v>
@@ -6655,13 +6659,13 @@
         <v>36</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>36</v>
@@ -6679,45 +6683,45 @@
         <v>36</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6725,34 +6729,34 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>36</v>
@@ -6801,34 +6805,34 @@
         <v>36</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>36</v>
@@ -6836,10 +6840,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6859,19 +6863,19 @@
         <v>36</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6921,7 +6925,7 @@
         <v>36</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>34</v>
@@ -6930,10 +6934,10 @@
         <v>35</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>36</v>
@@ -6942,13 +6946,13 @@
         <v>36</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>36</v>
@@ -6956,21 +6960,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>36</v>
@@ -6979,22 +6983,22 @@
         <v>36</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>36</v>
@@ -7043,34 +7047,34 @@
         <v>36</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>36</v>
@@ -7078,45 +7082,45 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>36</v>
@@ -7165,34 +7169,34 @@
         <v>36</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>36</v>
@@ -7200,10 +7204,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7214,7 +7218,7 @@
         <v>34</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>36</v>
@@ -7223,19 +7227,19 @@
         <v>36</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7285,19 +7289,19 @@
         <v>36</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>36</v>
@@ -7306,13 +7310,13 @@
         <v>36</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>36</v>
@@ -7320,10 +7324,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7343,22 +7347,22 @@
         <v>36</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>36</v>
@@ -7407,7 +7411,7 @@
         <v>36</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>34</v>
@@ -7416,25 +7420,25 @@
         <v>35</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>36</v>
@@ -7442,10 +7446,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7456,31 +7460,31 @@
         <v>34</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>36</v>
@@ -7490,7 +7494,7 @@
         <v>36</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>36</v>
@@ -7529,45 +7533,45 @@
         <v>36</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7578,7 +7582,7 @@
         <v>34</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>36</v>
@@ -7590,13 +7594,13 @@
         <v>36</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7647,13 +7651,13 @@
         <v>36</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>36</v>
@@ -7671,7 +7675,7 @@
         <v>36</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>36</v>
@@ -7682,14 +7686,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7708,16 +7712,16 @@
         <v>36</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7755,19 +7759,19 @@
         <v>36</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>34</v>
@@ -7776,10 +7780,10 @@
         <v>35</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>36</v>
@@ -7791,7 +7795,7 @@
         <v>36</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>36</v>
@@ -7802,10 +7806,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7816,7 +7820,7 @@
         <v>34</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>36</v>
@@ -7825,22 +7829,22 @@
         <v>36</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>36</v>
@@ -7889,19 +7893,19 @@
         <v>36</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>36</v>
@@ -7910,10 +7914,10 @@
         <v>36</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>36</v>
@@ -7924,10 +7928,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7938,94 +7942,94 @@
         <v>34</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I48" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Q48" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="R48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AH48" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="J48" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="Q48" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="R48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>46</v>
-      </c>
       <c r="AI48" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>36</v>
@@ -8034,10 +8038,10 @@
         <v>36</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>36</v>
@@ -8048,10 +8052,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8062,7 +8066,7 @@
         <v>34</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>36</v>
@@ -8071,22 +8075,22 @@
         <v>36</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>36</v>
@@ -8135,19 +8139,19 @@
         <v>36</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>36</v>
@@ -8156,10 +8160,10 @@
         <v>36</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>36</v>
@@ -8170,10 +8174,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8181,10 +8185,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>36</v>
@@ -8193,22 +8197,22 @@
         <v>36</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>36</v>
@@ -8257,19 +8261,19 @@
         <v>36</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>36</v>
@@ -8278,10 +8282,10 @@
         <v>36</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>36</v>
@@ -8292,10 +8296,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8303,10 +8307,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>36</v>
@@ -8315,22 +8319,22 @@
         <v>36</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>36</v>
@@ -8379,19 +8383,19 @@
         <v>36</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>36</v>
@@ -8400,10 +8404,10 @@
         <v>36</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>36</v>
@@ -8414,10 +8418,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8428,10 +8432,10 @@
         <v>34</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>36</v>
@@ -8440,19 +8444,19 @@
         <v>36</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>36</v>
@@ -8477,13 +8481,13 @@
         <v>36</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>36</v>
@@ -8501,19 +8505,19 @@
         <v>36</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>36</v>
@@ -8522,10 +8526,10 @@
         <v>36</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>36</v>
@@ -8536,10 +8540,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8550,7 +8554,7 @@
         <v>34</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>36</v>
@@ -8562,13 +8566,13 @@
         <v>36</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8619,13 +8623,13 @@
         <v>36</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>36</v>
@@ -8643,7 +8647,7 @@
         <v>36</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>36</v>
@@ -8654,14 +8658,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8680,16 +8684,16 @@
         <v>36</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8727,19 +8731,19 @@
         <v>36</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>34</v>
@@ -8748,10 +8752,10 @@
         <v>35</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>36</v>
@@ -8763,7 +8767,7 @@
         <v>36</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>36</v>
@@ -8774,10 +8778,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8797,22 +8801,22 @@
         <v>36</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>36</v>
@@ -8861,7 +8865,7 @@
         <v>36</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>34</v>
@@ -8870,10 +8874,10 @@
         <v>35</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>36</v>
@@ -8882,10 +8886,10 @@
         <v>36</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>36</v>
@@ -8896,10 +8900,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8910,7 +8914,7 @@
         <v>34</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>36</v>
@@ -8922,13 +8926,13 @@
         <v>36</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8979,13 +8983,13 @@
         <v>36</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>36</v>
@@ -9003,7 +9007,7 @@
         <v>36</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>36</v>
@@ -9014,14 +9018,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9040,16 +9044,16 @@
         <v>36</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9087,19 +9091,19 @@
         <v>36</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>34</v>
@@ -9108,10 +9112,10 @@
         <v>35</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>36</v>
@@ -9123,7 +9127,7 @@
         <v>36</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>36</v>
@@ -9134,10 +9138,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9145,10 +9149,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>36</v>
@@ -9157,22 +9161,22 @@
         <v>36</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>36</v>
@@ -9221,19 +9225,19 @@
         <v>36</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>36</v>
@@ -9242,10 +9246,10 @@
         <v>36</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>36</v>
@@ -9256,10 +9260,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9270,7 +9274,7 @@
         <v>34</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>36</v>
@@ -9279,19 +9283,19 @@
         <v>36</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9341,19 +9345,19 @@
         <v>36</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>36</v>
@@ -9362,10 +9366,10 @@
         <v>36</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>36</v>
@@ -9376,10 +9380,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9387,10 +9391,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>36</v>
@@ -9399,22 +9403,22 @@
         <v>36</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>36</v>
@@ -9463,19 +9467,19 @@
         <v>36</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>36</v>
@@ -9484,10 +9488,10 @@
         <v>36</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>36</v>
@@ -9498,10 +9502,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9512,7 +9516,7 @@
         <v>34</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>36</v>
@@ -9521,22 +9525,22 @@
         <v>36</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>36</v>
@@ -9585,19 +9589,19 @@
         <v>36</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>36</v>
@@ -9606,10 +9610,10 @@
         <v>36</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>36</v>
@@ -9620,10 +9624,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9634,7 +9638,7 @@
         <v>34</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>36</v>
@@ -9643,22 +9647,22 @@
         <v>36</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>36</v>
@@ -9707,19 +9711,19 @@
         <v>36</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>36</v>
@@ -9728,10 +9732,10 @@
         <v>36</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>36</v>
@@ -9742,10 +9746,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9756,7 +9760,7 @@
         <v>34</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>36</v>
@@ -9765,22 +9769,22 @@
         <v>36</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>36</v>
@@ -9829,19 +9833,19 @@
         <v>36</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>36</v>
@@ -9850,10 +9854,10 @@
         <v>36</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>36</v>
@@ -9864,14 +9868,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9890,19 +9894,19 @@
         <v>36</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>36</v>
@@ -9927,13 +9931,13 @@
         <v>36</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>36</v>
@@ -9951,7 +9955,7 @@
         <v>36</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>34</v>
@@ -9960,36 +9964,36 @@
         <v>35</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10012,19 +10016,19 @@
         <v>36</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>36</v>
@@ -10073,7 +10077,7 @@
         <v>36</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>34</v>
@@ -10082,10 +10086,10 @@
         <v>35</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>36</v>
@@ -10094,10 +10098,10 @@
         <v>36</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>36</v>
@@ -10108,10 +10112,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10122,7 +10126,7 @@
         <v>34</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>36</v>
@@ -10134,16 +10138,16 @@
         <v>36</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10169,13 +10173,13 @@
         <v>36</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>36</v>
@@ -10193,45 +10197,45 @@
         <v>36</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10242,7 +10246,7 @@
         <v>34</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>36</v>
@@ -10254,19 +10258,19 @@
         <v>36</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>36</v>
@@ -10291,13 +10295,13 @@
         <v>36</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>36</v>
@@ -10315,19 +10319,19 @@
         <v>36</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>36</v>
@@ -10336,10 +10340,10 @@
         <v>36</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>36</v>
@@ -10350,10 +10354,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10364,7 +10368,7 @@
         <v>34</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>36</v>
@@ -10376,16 +10380,16 @@
         <v>36</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10435,45 +10439,45 @@
         <v>36</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10484,7 +10488,7 @@
         <v>34</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>36</v>
@@ -10496,16 +10500,16 @@
         <v>36</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10555,45 +10559,45 @@
         <v>36</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10616,19 +10620,19 @@
         <v>36</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>36</v>
@@ -10677,7 +10681,7 @@
         <v>36</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>34</v>
@@ -10686,10 +10690,10 @@
         <v>35</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>36</v>
@@ -10698,10 +10702,10 @@
         <v>36</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>36</v>
@@ -10712,10 +10716,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10726,7 +10730,7 @@
         <v>34</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>36</v>
@@ -10738,13 +10742,13 @@
         <v>36</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10795,13 +10799,13 @@
         <v>36</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>36</v>
@@ -10819,7 +10823,7 @@
         <v>36</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>36</v>
@@ -10830,14 +10834,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10856,16 +10860,16 @@
         <v>36</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10903,19 +10907,19 @@
         <v>36</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>34</v>
@@ -10924,10 +10928,10 @@
         <v>35</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>36</v>
@@ -10939,7 +10943,7 @@
         <v>36</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>36</v>
@@ -10950,14 +10954,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10970,25 +10974,25 @@
         <v>36</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>36</v>
@@ -11037,7 +11041,7 @@
         <v>36</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>34</v>
@@ -11046,10 +11050,10 @@
         <v>35</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>36</v>
@@ -11061,7 +11065,7 @@
         <v>36</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>36</v>
@@ -11072,10 +11076,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11086,7 +11090,7 @@
         <v>34</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>36</v>
@@ -11098,16 +11102,16 @@
         <v>36</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11157,19 +11161,19 @@
         <v>36</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>36</v>
@@ -11178,10 +11182,10 @@
         <v>36</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>36</v>
@@ -11192,10 +11196,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11206,7 +11210,7 @@
         <v>34</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>36</v>
@@ -11218,16 +11222,16 @@
         <v>36</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11277,19 +11281,19 @@
         <v>36</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>36</v>
@@ -11298,10 +11302,10 @@
         <v>36</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>36</v>
@@ -11312,10 +11316,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11326,7 +11330,7 @@
         <v>34</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>36</v>
@@ -11338,19 +11342,19 @@
         <v>36</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>36</v>
@@ -11375,13 +11379,13 @@
         <v>36</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>36</v>
@@ -11399,31 +11403,31 @@
         <v>36</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>36</v>
@@ -11434,10 +11438,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11460,19 +11464,19 @@
         <v>36</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>36</v>
@@ -11497,13 +11501,13 @@
         <v>36</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>36</v>
@@ -11521,7 +11525,7 @@
         <v>36</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>34</v>
@@ -11530,22 +11534,22 @@
         <v>35</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>36</v>
@@ -11556,10 +11560,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11570,7 +11574,7 @@
         <v>34</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>36</v>
@@ -11582,19 +11586,19 @@
         <v>36</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>36</v>
@@ -11643,19 +11647,19 @@
         <v>36</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>36</v>
@@ -11664,10 +11668,10 @@
         <v>36</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>36</v>
@@ -11678,10 +11682,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11692,7 +11696,7 @@
         <v>34</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>36</v>
@@ -11704,16 +11708,16 @@
         <v>36</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11763,19 +11767,19 @@
         <v>36</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>36</v>
@@ -11784,10 +11788,10 @@
         <v>36</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>36</v>
@@ -11798,10 +11802,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11821,19 +11825,19 @@
         <v>36</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11883,7 +11887,7 @@
         <v>36</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>34</v>
@@ -11892,10 +11896,10 @@
         <v>35</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>36</v>
@@ -11904,10 +11908,10 @@
         <v>36</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>36</v>
@@ -11918,10 +11922,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11941,19 +11945,19 @@
         <v>36</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12003,7 +12007,7 @@
         <v>36</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>34</v>
@@ -12012,10 +12016,10 @@
         <v>35</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>36</v>
@@ -12024,10 +12028,10 @@
         <v>36</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>36</v>
@@ -12038,10 +12042,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12055,28 +12059,28 @@
         <v>35</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>36</v>
@@ -12125,7 +12129,7 @@
         <v>36</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>34</v>
@@ -12134,10 +12138,10 @@
         <v>35</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>36</v>
@@ -12146,10 +12150,10 @@
         <v>36</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>36</v>
@@ -12160,10 +12164,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12174,7 +12178,7 @@
         <v>34</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>36</v>
@@ -12186,13 +12190,13 @@
         <v>36</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12243,13 +12247,13 @@
         <v>36</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>36</v>
@@ -12267,7 +12271,7 @@
         <v>36</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>36</v>
@@ -12278,14 +12282,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12304,16 +12308,16 @@
         <v>36</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12351,19 +12355,19 @@
         <v>36</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>34</v>
@@ -12372,10 +12376,10 @@
         <v>35</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>36</v>
@@ -12387,7 +12391,7 @@
         <v>36</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>36</v>
@@ -12398,14 +12402,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12418,25 +12422,25 @@
         <v>36</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>36</v>
@@ -12485,7 +12489,7 @@
         <v>36</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>34</v>
@@ -12494,10 +12498,10 @@
         <v>35</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>36</v>
@@ -12509,7 +12513,7 @@
         <v>36</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>36</v>
@@ -12520,10 +12524,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12531,34 +12535,34 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>36</v>
@@ -12583,13 +12587,13 @@
         <v>36</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>36</v>
@@ -12607,34 +12611,34 @@
         <v>36</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>36</v>
@@ -12642,10 +12646,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12656,31 +12660,31 @@
         <v>34</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>36</v>
@@ -12705,13 +12709,13 @@
         <v>36</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>36</v>
@@ -12729,45 +12733,45 @@
         <v>36</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12778,10 +12782,10 @@
         <v>34</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>36</v>
@@ -12790,19 +12794,19 @@
         <v>36</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>36</v>
@@ -12827,13 +12831,13 @@
         <v>36</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>36</v>
@@ -12851,19 +12855,19 @@
         <v>36</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>36</v>
@@ -12872,10 +12876,10 @@
         <v>36</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>36</v>
@@ -12886,14 +12890,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12912,19 +12916,19 @@
         <v>36</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>36</v>
@@ -12949,13 +12953,13 @@
         <v>36</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>36</v>
@@ -12973,7 +12977,7 @@
         <v>36</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>34</v>
@@ -12982,36 +12986,36 @@
         <v>35</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13037,16 +13041,16 @@
         <v>37</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>36</v>
@@ -13095,7 +13099,7 @@
         <v>36</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>34</v>
@@ -13116,10 +13120,10 @@
         <v>36</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>36</v>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:09:26+00:00</t>
+    <t>2023-09-19T16:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:18:04+00:00</t>
+    <t>2023-09-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:08:45+00:00</t>
+    <t>2023-09-27T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:45:14+00:00</t>
+    <t>2023-11-23T10:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3533" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3533" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-23T10:14:09+00:00</t>
+    <t>2023-11-28T12:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -3399,10 +3402,10 @@
         <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3452,7 +3455,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3487,10 +3490,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3513,16 +3516,16 @@
         <v>92</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3572,7 +3575,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3607,10 +3610,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3633,16 +3636,16 @@
         <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3668,13 +3671,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3692,7 +3695,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3713,10 +3716,10 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>80</v>
@@ -3727,10 +3730,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3753,16 +3756,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3788,13 +3791,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3812,7 +3815,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3833,10 +3836,10 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -3847,10 +3850,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3876,13 +3879,13 @@
         <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3932,7 +3935,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3967,10 +3970,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3993,16 +3996,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4028,13 +4031,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -4052,7 +4055,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -4087,14 +4090,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4113,16 +4116,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4172,7 +4175,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4196,7 +4199,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -4207,14 +4210,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4233,16 +4236,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4292,7 +4295,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4327,10 +4330,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4359,7 +4362,7 @@
         <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>117</v>
@@ -4412,7 +4415,7 @@
         <v>120</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4447,13 +4450,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>80</v>
@@ -4475,13 +4478,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4532,7 +4535,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4567,13 +4570,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>80</v>
@@ -4595,13 +4598,13 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4652,7 +4655,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4687,10 +4690,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4716,16 +4719,16 @@
         <v>114</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4774,7 +4777,7 @@
         <v>120</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4809,10 +4812,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4835,17 +4838,17 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4894,7 +4897,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4909,19 +4912,19 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4929,14 +4932,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4955,19 +4958,19 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5016,7 +5019,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5028,19 +5031,19 @@
         <v>103</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -5051,14 +5054,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5077,16 +5080,16 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5136,7 +5139,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5148,19 +5151,19 @@
         <v>103</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -5171,10 +5174,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5197,19 +5200,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5234,13 +5237,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -5258,7 +5261,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>91</v>
@@ -5273,19 +5276,19 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5293,10 +5296,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5319,19 +5322,19 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5356,19 +5359,19 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5378,7 +5381,7 @@
         <v>120</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5399,13 +5402,13 @@
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5413,13 +5416,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>80</v>
@@ -5441,19 +5444,19 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5478,13 +5481,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -5502,7 +5505,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5523,13 +5526,13 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
@@ -5537,10 +5540,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5655,10 +5658,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5775,10 +5778,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5801,19 +5804,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5862,7 +5865,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5883,10 +5886,10 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
@@ -5897,10 +5900,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6015,10 +6018,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6135,10 +6138,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6164,23 +6167,23 @@
         <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>80</v>
@@ -6222,7 +6225,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6243,10 +6246,10 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -6257,10 +6260,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6286,13 +6289,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6342,7 +6345,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6363,10 +6366,10 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6377,10 +6380,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6403,26 +6406,26 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>80</v>
@@ -6464,7 +6467,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6485,10 +6488,10 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6499,10 +6502,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6528,16 +6531,16 @@
         <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6586,7 +6589,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6607,10 +6610,10 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6621,10 +6624,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6647,19 +6650,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6708,7 +6711,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6729,10 +6732,10 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6743,10 +6746,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6772,16 +6775,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6830,7 +6833,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6851,10 +6854,10 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6865,14 +6868,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6891,19 +6894,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6913,7 +6916,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6928,13 +6931,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6952,7 +6955,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -6967,30 +6970,30 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7013,19 +7016,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -7074,7 +7077,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7086,22 +7089,22 @@
         <v>103</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -7109,10 +7112,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7135,16 +7138,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7194,7 +7197,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7206,7 +7209,7 @@
         <v>103</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -7215,13 +7218,13 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -7229,14 +7232,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7255,19 +7258,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7316,7 +7319,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7328,22 +7331,22 @@
         <v>103</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -7351,14 +7354,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7377,19 +7380,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7438,7 +7441,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7447,25 +7450,25 @@
         <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7473,10 +7476,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7502,13 +7505,13 @@
         <v>129</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7558,7 +7561,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7579,13 +7582,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7593,10 +7596,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7619,19 +7622,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7680,7 +7683,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7692,22 +7695,22 @@
         <v>103</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7715,10 +7718,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7741,19 +7744,19 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7763,7 +7766,7 @@
         <v>80</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>80</v>
@@ -7802,7 +7805,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7811,7 +7814,7 @@
         <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>104</v>
@@ -7820,27 +7823,27 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7955,10 +7958,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8075,10 +8078,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8101,19 +8104,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -8162,7 +8165,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8183,10 +8186,10 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -8197,10 +8200,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8223,25 +8226,25 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R49" t="s" s="2">
         <v>80</v>
@@ -8262,13 +8265,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -8286,7 +8289,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8307,10 +8310,10 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -8321,10 +8324,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8350,16 +8353,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8408,7 +8411,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8429,10 +8432,10 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8443,10 +8446,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8472,16 +8475,16 @@
         <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8530,7 +8533,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8539,7 +8542,7 @@
         <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
@@ -8551,10 +8554,10 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8565,10 +8568,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8591,19 +8594,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8652,7 +8655,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8673,10 +8676,10 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8687,10 +8690,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8713,19 +8716,19 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8750,13 +8753,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8774,7 +8777,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8783,7 +8786,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>104</v>
@@ -8798,7 +8801,7 @@
         <v>105</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8809,10 +8812,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8927,10 +8930,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9047,10 +9050,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9073,19 +9076,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -9134,7 +9137,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9155,10 +9158,10 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -9169,10 +9172,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9287,10 +9290,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9407,10 +9410,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9436,16 +9439,16 @@
         <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9494,7 +9497,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9515,10 +9518,10 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
@@ -9529,10 +9532,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9558,13 +9561,13 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9614,7 +9617,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9635,10 +9638,10 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9649,10 +9652,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9675,19 +9678,19 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9736,7 +9739,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9757,10 +9760,10 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9771,10 +9774,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9800,16 +9803,16 @@
         <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9858,7 +9861,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9879,10 +9882,10 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9893,10 +9896,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9919,19 +9922,19 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9980,7 +9983,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10001,10 +10004,10 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -10015,10 +10018,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10044,16 +10047,16 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -10102,7 +10105,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10123,10 +10126,10 @@
         <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -10137,14 +10140,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10163,19 +10166,19 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -10200,13 +10203,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -10224,7 +10227,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10242,27 +10245,27 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10285,19 +10288,19 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -10346,7 +10349,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10367,10 +10370,10 @@
         <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10381,10 +10384,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10407,16 +10410,16 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10442,13 +10445,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10466,7 +10469,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10484,27 +10487,27 @@
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10527,19 +10530,19 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10564,13 +10567,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10588,7 +10591,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10609,10 +10612,10 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -10623,10 +10626,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10649,16 +10652,16 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10708,7 +10711,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10720,33 +10723,33 @@
         <v>103</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10769,16 +10772,16 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10828,7 +10831,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10840,33 +10843,33 @@
         <v>103</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10889,19 +10892,19 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10950,7 +10953,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10962,7 +10965,7 @@
         <v>103</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10971,10 +10974,10 @@
         <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10985,10 +10988,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11103,10 +11106,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11223,14 +11226,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11252,16 +11255,16 @@
         <v>114</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -11310,7 +11313,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11345,10 +11348,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11371,16 +11374,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11430,7 +11433,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11439,10 +11442,10 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
@@ -11451,10 +11454,10 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11465,10 +11468,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11491,16 +11494,16 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11550,7 +11553,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11559,10 +11562,10 @@
         <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
@@ -11571,10 +11574,10 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11585,10 +11588,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11611,19 +11614,19 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11648,13 +11651,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11672,7 +11675,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11690,13 +11693,13 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -11707,10 +11710,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11733,19 +11736,19 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11770,13 +11773,13 @@
         <v>80</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>80</v>
@@ -11794,7 +11797,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11812,13 +11815,13 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11829,10 +11832,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11855,19 +11858,19 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11916,7 +11919,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11928,7 +11931,7 @@
         <v>103</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11937,10 +11940,10 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -11951,10 +11954,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11980,13 +11983,13 @@
         <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12036,7 +12039,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12057,10 +12060,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12071,10 +12074,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12097,16 +12100,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12156,7 +12159,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12168,7 +12171,7 @@
         <v>103</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>80</v>
@@ -12177,10 +12180,10 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12191,10 +12194,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12217,16 +12220,16 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12276,7 +12279,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12288,7 +12291,7 @@
         <v>103</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>80</v>
@@ -12297,10 +12300,10 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12311,10 +12314,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12337,19 +12340,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12398,7 +12401,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12410,7 +12413,7 @@
         <v>103</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
@@ -12419,10 +12422,10 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12433,10 +12436,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12551,10 +12554,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12671,14 +12674,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12700,16 +12703,16 @@
         <v>114</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12758,7 +12761,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12793,10 +12796,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12819,19 +12822,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12856,13 +12859,13 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -12880,7 +12883,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>91</v>
@@ -12898,16 +12901,16 @@
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12915,10 +12918,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12941,19 +12944,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -12978,13 +12981,13 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -13002,7 +13005,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13011,7 +13014,7 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>104</v>
@@ -13020,27 +13023,27 @@
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13063,19 +13066,19 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -13100,13 +13103,13 @@
         <v>80</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -13124,7 +13127,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13133,7 +13136,7 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>104</v>
@@ -13148,7 +13151,7 @@
         <v>105</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -13159,14 +13162,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13185,19 +13188,19 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13222,13 +13225,13 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13246,7 +13249,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13264,27 +13267,27 @@
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13310,16 +13313,16 @@
         <v>81</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13368,7 +13371,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13389,10 +13392,10 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:14:54+00:00</t>
+    <t>2023-11-28T12:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:15:35+00:00</t>
+    <t>2023-11-28T12:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:22:20+00:00</t>
+    <t>2023-11-28T12:44:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:44:29+00:00</t>
+    <t>2023-11-28T13:07:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:07:26+00:00</t>
+    <t>2023-11-28T13:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1687,12 +1687,11 @@
 </t>
   </si>
   <si>
-    <t>Dispositif utilisé pour l'observation</t>
-  </si>
-  <si>
     <t>Dispositif utilisé pour l'observation
-Si la mesure a été faite par un objet connecté (Profil PhdDevice)
-=&gt;cette référence est obligatoire</t>
+Si la mesure a été faite par un objet connecté (Profil PhdDevice), cette référence est obligatoire</t>
+  </si>
+  <si>
+    <t>The device used to generate the observation data.</t>
   </si>
   <si>
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
@@ -10763,7 +10762,7 @@
         <v>91</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:18:47+00:00</t>
+    <t>2023-11-28T13:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:27:45+00:00</t>
+    <t>2023-11-28T13:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:42:11+00:00</t>
+    <t>2023-12-08T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T10:33:05+00:00</t>
+    <t>2023-12-29T10:04:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:04:05+00:00</t>
+    <t>2024-02-01T10:35:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T10:35:02+00:00</t>
+    <t>2024-02-01T13:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:55:30+00:00</t>
+    <t>2024-02-01T13:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:56:11+00:00</t>
+    <t>2024-02-01T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T14:29:51+00:00</t>
+    <t>2024-02-01T16:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T16:04:25+00:00</t>
+    <t>2024-02-05T14:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:48:49+00:00</t>
+    <t>2024-02-12T14:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:46:58+00:00</t>
+    <t>2024-02-12T14:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:53:29+00:00</t>
+    <t>2024-04-08T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
